--- a/data/metadata_raw/registered_crimes.xlsx
+++ b/data/metadata_raw/registered_crimes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="212">
   <si>
     <t>Code</t>
   </si>
@@ -77,6 +77,9 @@
     <t>2024</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>1700</t>
   </si>
   <si>
@@ -521,7 +524,7 @@
     <t>2022-07-05</t>
   </si>
   <si>
-    <t>2025-05-06</t>
+    <t>2026-04-22</t>
   </si>
   <si>
     <t>2.04.09.0001</t>
@@ -1018,10 +1021,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,22 +1085,25 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2">
         <v>90050</v>
@@ -1144,22 +1150,25 @@
       <c r="T2">
         <v>132298</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2">
+        <v>155002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3">
         <v>3182</v>
@@ -1206,22 +1215,25 @@
       <c r="T3">
         <v>4673</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3">
+        <v>5117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4">
         <v>5716</v>
@@ -1268,22 +1280,25 @@
       <c r="T4">
         <v>8743</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4">
+        <v>10784</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5">
         <v>4349</v>
@@ -1330,22 +1345,25 @@
       <c r="T5">
         <v>7489</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5">
+        <v>8009</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>2462</v>
@@ -1392,22 +1410,25 @@
       <c r="T6">
         <v>4288</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6">
+        <v>5231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7">
         <v>5535</v>
@@ -1454,22 +1475,25 @@
       <c r="T7">
         <v>7841</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7">
+        <v>9875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8">
         <v>3357</v>
@@ -1516,22 +1540,25 @@
       <c r="T8">
         <v>4120</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="U8">
+        <v>4887</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F9">
         <v>5686</v>
@@ -1578,22 +1605,25 @@
       <c r="T9">
         <v>8204</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="U9">
+        <v>12410</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10">
         <v>7739</v>
@@ -1640,22 +1670,25 @@
       <c r="T10">
         <v>9402</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10">
+        <v>15998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11">
         <v>3941</v>
@@ -1702,22 +1735,25 @@
       <c r="T11">
         <v>8001</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11">
+        <v>10015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F12">
         <v>2925</v>
@@ -1764,22 +1800,25 @@
       <c r="T12">
         <v>3295</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F13">
         <v>9725</v>
@@ -1826,22 +1865,25 @@
       <c r="T13">
         <v>14702</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13">
+        <v>16883</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F14">
         <v>8985</v>
@@ -1888,22 +1930,25 @@
       <c r="T14">
         <v>14289</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14">
+        <v>15257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F15">
         <v>3489</v>
@@ -1950,22 +1995,25 @@
       <c r="T15">
         <v>4339</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F16">
         <v>21061</v>
@@ -2011,6 +2059,9 @@
       </c>
       <c r="T16">
         <v>32106</v>
+      </c>
+      <c r="U16">
+        <v>30600</v>
       </c>
     </row>
   </sheetData>
@@ -2025,444 +2076,444 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
